--- a/ValueSet-VaccineCovid19Icd11ValueSet.xlsx
+++ b/ValueSet-VaccineCovid19Icd11ValueSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-30T07:55:09+00:00</t>
+    <t>2024-07-30T11:13:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
